--- a/Result/checksun_type/貨櫃運輸集散及倉儲.xlsx
+++ b/Result/checksun_type/貨櫃運輸集散及倉儲.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>107.35</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>109.25</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>107.35</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>109.25</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>50407017.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>44881055.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>44881055</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>48430759.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>53475051.56</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>53475051.56</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1187039.950376511</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>50407017</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>50407017.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>106.6</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>107.38</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>109.33</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>107.38</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>109.33</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>30199167.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>41336950.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>41336950.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>46688175.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>53094931.02</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>53094931.02</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1695099.485860117</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>30199167</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>30199167.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>106.4</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>107.45</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>109.45</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>109.45</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>59441164.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>51851718.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>51851718.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>47623529.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>53054880.8</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>53054880.8</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-195232.7691988423</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>59441164</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>59441164.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>106.2</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>107.55</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>109.57</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>109.57</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>51587654.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>54373269.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>54373269.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>44799514.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>52486749.48</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>52486749.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1178664.539354198</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>51587654</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>51587654.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>106.4</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>107.78</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>109.7</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>107.78</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>109.7</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>32770273.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>53461884.0</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>53461884</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>42039148.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>51785780.4</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>51785780.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1700024.406027772</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>32770273</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>32770273.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>106.7</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>108.0</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>109.83</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>108</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>109.83</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>32686495.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>51980464.0</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>51980464</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>46974524.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>51759630.14</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>51759630.14</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-367961.0939176083</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>32686495</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>32686495.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>108.2</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>109.97</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>109.97</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>82773006.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>52039400.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>52039400.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>53395922.5</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>51511000.34</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>51511000.34</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>1557104.176736824</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>82773006</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>82773006.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>108.35</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>110.08</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>110.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>72048921.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>43395339.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>43395339.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>51979182.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>50578133.74</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>50578133.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1114825.335783154</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>72048921</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>72048921.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>107.5</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>108.42</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>110.19</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>108.42</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>110.19</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>47030725.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>35225759.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>35225759.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>49593484.7</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>49702151.84</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>49702151.84</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-3743043.198819436</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>47030725</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>47030725.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>107.7</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>108.45</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>110.27</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>110.27</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>25363173.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>30616413.0</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>30616413</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>47656295.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>49539295.04</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>49539295.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-4683439.031770572</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>25363173</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>25363173.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>107.9</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>108.42</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>110.35</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>108.42</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>110.35</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>32981176.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>41968585.0</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>41968585</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>50335158.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>49448278.74</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>49448278.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-3538072.541994669</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>32981176</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>32981176.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>47.51000000000001</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>48.56</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.27</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>48.56</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.27</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>14671687.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>16643498.8</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>16643498.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>20266035.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>23240734.28</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>23240734.28</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-2027321.100493923</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>14671687</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>14671687.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>47.15</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>48.54</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.31</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>14480184.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>16118133.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>16118133.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>20128000.8</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>23809342.8</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>23809342.8</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-1857813.292244852</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>14480184</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>14480184.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>47.07</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>48.59</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>49.4</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>49.4</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>15210476.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>18220452.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>18220452.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>21527916.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>24157689.22</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>24157689.22</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-1528790.62716601</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>15210476</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>15210476.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>47.12</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>48.71</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>49.5</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>48.71</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>49.5</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>21910331.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>23606734.8</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>23606734.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>23666612.3</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>24673033.24</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>24673033.24</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-1082404.154654589</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>21910331</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>21910331.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>47.5</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>48.85</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>49.6</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>48.85</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>49.6</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>16944816.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>21785266.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>21785266.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>30603029.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>25584038.76</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>25584038.76</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-1123893.509829178</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>16944816</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>16944816.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>47.61</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>48.94</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>49.68</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>48.94</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>49.68</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>12044860.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>23888572.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>23888572.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>30373185.4</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>26127223.16</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>26127223.16</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-611005.4990132637</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>12044860</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>12044860.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>48.2</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>49.79</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>49.09</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>49.79</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>24991780.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>24137868.2</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>24137868.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>30887125.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>26839124.58</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>26839124.58</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>668508.5699742287</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>24991780</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>24991780.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>48.72</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>49.24</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>49.89</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>49.24</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>49.89</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>42141887.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>24835380.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>24835380.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>30062483.3</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>26895965.08</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>26895965.08</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>1085340.505314421</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>42141887</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>42141887.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>49.29000000000001</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>49.35</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>49.98</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>49.98</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>12802990.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>23726489.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>23726489.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>28540342.5</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>26841362.6</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>26841362.6</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-195458.9265322462</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>12802990</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>12802990.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>49.79000000000001</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.38</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>50.03</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.38</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>50.03</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>27461346.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>39420793.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>39420793.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>28212581.1</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>27370045.38</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>27370045.38</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>1125261.525348667</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>27461346</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>27461346.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.07000000000001</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.42</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>50.08</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.42</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>50.08</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>13291338.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>36857798.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>36857798.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>27672188.8</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>27877775.08</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>27877775.08</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>1401278.973558951</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>13291338</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>13291338.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>19.26</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>19.26</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>1116.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>970.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>970</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>1055.2</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>1295.54</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>1295.54</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-67.631683372314</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>1116</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>1116.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>18.99</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>19.28</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>19.28</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>611.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>834.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>834.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>1206.3</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>1300.46</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>1300.46</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-85.7483196355438</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>611</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>611.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>19.31</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>1158.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>951.4</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>951.4</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>1277.2</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>1309.6</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>1309.6</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-54.45964573888818</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>1158</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>1158.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>19.01</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>19.33</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>19.33</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>800.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>1132.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>1132.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>1255.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>1310.02</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>1310.02</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-66.42369568156278</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>800</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>800.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>19.0</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>19.36</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>1165.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>1129.6</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>1129.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>1236.8</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>1322.42</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>1322.42</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-42.78577789675637</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>1165</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>1165.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>18.95</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>18.85</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>19.39</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>18.85</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>19.39</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>439.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>1140.4</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>1140.4</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>1189.8</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>1320.76</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>1320.76</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-46.59640327929151</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>439</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>439.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>18.85</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>19.42</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>1195.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>1578.0</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>1578</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>1344.1</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>1331.36</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>1331.36</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>27.40971771991872</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>1195</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>1195.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>18.78</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>18.86</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>19.44</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19.44</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>2065.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>1603.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>1603</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>1331.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>1330.72</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>1330.72</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>51.15382922879326</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>2065</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>2065.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>18.68</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>18.88</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>18.88</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>19.47</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>784.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>1377.4</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>1377.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>1335.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>1319.4</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>1319.4</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-9.967219659557031</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>784</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>784.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>18.62</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>18.91</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>19.49</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>18.91</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>19.49</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>1219.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>1344.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>1344</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>1302.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>1330.1</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>1330.1</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>40.32296834492672</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>1219</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>1219.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>18.62</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>18.95</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>19.52</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>2627.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>1239.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>1239.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>1319.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1323.4</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1323.4</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>64.11884519615614</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>2627</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>2627.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>37.32000000000001</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>37.81</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>37.85</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>37.85</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>222.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>228.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>228.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>141.2</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>0</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>18.88167784402989</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>222</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>222.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>37.44</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>37.84</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>37.84</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>37.86</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>408.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>199.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>199.4</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>122.8</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>0</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>19.00956991673598</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>408</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>408.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>37.55</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>37.88</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>37.88</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>252.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>132.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>132.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>89.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>0</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-1.415211762138739</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>252</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>252.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>37.78</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>37.89</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>37.89</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>223.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>90</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>68.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>0</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-13.82864231188337</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>223</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>223.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,21 +16967,17 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
+      <c r="AM39" t="n">
+        <v>37.92</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="AO39" t="inlineStr">
         <is>
           <t>37.92</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>37.92</t>
-        </is>
-      </c>
       <c r="AP39" t="inlineStr">
         <is>
           <t>-70.01</t>
@@ -17244,20 +17018,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>53.0</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>53</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>79.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>0</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-27.96109158609416</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>38</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,21 +17397,17 @@
           <t>38.17999999999999</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
+      <c r="AM40" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.91</v>
+      </c>
+      <c r="AO40" t="inlineStr">
         <is>
           <t>37.93</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
       <c r="AP40" t="inlineStr">
         <is>
           <t>24.90</t>
@@ -17680,20 +17448,16 @@
           <t>76.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>53.8</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>140.5</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>0</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-27.33026584974905</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>76</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>38.26000000000001</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>37.94</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.91</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>75.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>46.2</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>46.2</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>136.7</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>0</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-29.52443387462218</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>75</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>38.28</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>37.95</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.91</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>37.95</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.91</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>46.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>46.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>0</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-31.49737270034728</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>38</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>38.15</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>37.93</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.9</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>37.93</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.9</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>46.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>46.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>0</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-29.22666485494216</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>38</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>37.95</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>37.89</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>37.89</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>37.89</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>106.8</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>106.8</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>0</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-24.93898704525833</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>42</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>42.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>37.84</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>37.86</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>37.89</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>37.89</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>38.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>227.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>227.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>0</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-18.35162635123652</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>38</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>38.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>49.23</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>50.01</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>50.01</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>53.7</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>331954463.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>249285624.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>249285624.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>171373999.3</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>326997419.26</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>326997419.26</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>13314160.3089878</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>331954463</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>331954463.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>47.69</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>49.87</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>475812516.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>196967092.0</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>196967092</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>147184502.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>332134322.56</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>332134322.56</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>5189911.259646922</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>475812516</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>475812516.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>47.22</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>50.03</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>54.25</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>50.03</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>54.25</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>333156841.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>117198674.6</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>117198674.6</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>111769421.8</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>342078852.16</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>342078852.16</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-22014875.60582745</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>333156841</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>333156841.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>47.17999999999999</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>54.62</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>54.62</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>58522058.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>67531722.0</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>67531722</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>93463829.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>351522194.38</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>351522194.38</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-44808074.67772558</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>58522058</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>58522058.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>47.75</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>50.69</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>55.02</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>50.69</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>55.02</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>46982246.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>84505208.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>84505208.40000001</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>100483736.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>370330610.32</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>370330610.32</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-46344343.9348041</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>46982246</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>46982246.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>48.02</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>51.04</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>55.42</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>55.42</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>70361799.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>93462373.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>93462373.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>119079003.2</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>390082646.5</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>390082646.5</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-45647450.73295899</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>70361799</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>70361799.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>48.68</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>51.46</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>55.87</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>55.87</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>76970429.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>97401913.8</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>97401913.8</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>182245214.5</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>439978926.18</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>439978926.18</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-45526575.02557456</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>76970429</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>76970429.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>49.01000000000001</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>51.83</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>56.38</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>56.38</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>84822078.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>106340169.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>106340169</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>260804200.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>449166959.54</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>449166959.54</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-44436013.83554062</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>84822078</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>84822078.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>49.23</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>52.24</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>56.74</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>52.24</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>56.74</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>143389490.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>119395936.8</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>119395936.8</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>281973501.5</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>453060434.38</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>453060434.38</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-42132316.89136565</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>143389490</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>143389490.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>49.53</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>52.68</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>57.11</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>57.11</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>91768073.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>116462264.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>116462264.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>276462754.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>460145932.38</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>460145932.38</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-43611675.51070979</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>91768073</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>91768073.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>50.14</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>53.04</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>57.41</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>53.04</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>57.41</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>90059499.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>144695632.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>144695632.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>277639700.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>464989232.82</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>464989232.82</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-38636619.02010462</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>90059499</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>90059499.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>13.59</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>13.92</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>14.2</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>14.2</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>746018.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>886803.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>886803.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>1428362.4</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>928007.14</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>928007.14</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-43405.48138256627</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>746018</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>746018.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>13.6</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>13.95</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>14.22</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>14.22</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>566106.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>1042475.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>1042475.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>1456718.6</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>948319.72</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>948319.72</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-13137.11027664901</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>566106</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>566106.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>13.62</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>13.98</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>14.24</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>13.98</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>14.24</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>881496.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>1530610.4</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>1530610.4</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>1470295.9</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>950268.5</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>950268.5</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>49848.88809882733</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>881496</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>881496.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>13.7</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>14.01</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>14.26</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>14.01</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>14.26</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>780635.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>1690790.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>1690790</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>1500639.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>946822.34</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>946822.34</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>104256.7826316927</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>780635</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>780635.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>13.82</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>14.05</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>14.28</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>14.28</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1459764.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>2002272.6</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>2002272.6</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>1486944.5</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>975304.08</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>975304.08</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>189065.4254417969</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1459764</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1459764.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>13.9</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>14.08</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>14.31</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>14.31</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>1524375.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>1969921.0</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>1969921</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>1423276.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>1014037.46</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>1014037.46</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>230704.4714047387</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>1524375</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>1524375.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>13.96</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>14.11</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>14.32</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>14.32</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>3006782.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>1870962.0</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>1870962</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>1369601.0</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>1001548.82</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>1001548.82</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>275026.7702302008</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>3006782</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>3006782.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,21 +27717,17 @@
           <t>14.01</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>14.14</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
+      <c r="AM64" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="AO64" t="inlineStr">
         <is>
           <t>14.34</t>
         </is>
       </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
-      </c>
       <c r="AP64" t="inlineStr">
         <is>
           <t>-3.57</t>
@@ -28144,20 +27768,16 @@
           <t>1682394.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>1409981.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>1409981.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>1158133.9</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>970395.6</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>970395.6</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>169692.633901211</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>1682394</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>1682394.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>14.02</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>14.34</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>14.34</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>2338048.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>1310489.8</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>1310489.8</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>1044737.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>945118.18</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>945118.1800000001</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>155053.5593633249</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>2338048</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>2338048.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>13.99</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>14.15</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>14.15</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>14.35</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>1298006.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>971616.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>971616.4</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>880389.1</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>917483.72</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>917483.72</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>58354.32576051191</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>1298006</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>1298006.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>14.0</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>14.16</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>14.35</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>14.35</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>1029580.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>876631.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>876631.4</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>862752.2</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>908015.94</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>908015.9399999999</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>29561.55183647503</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>1029580</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>1029580.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>24.05</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>24.72</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>24.72</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>25.16</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>22368251.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>12617559.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>12617559.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>13547566.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>20560463.78</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>20560463.78</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-1153640.137408298</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>22368251</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>22368251.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>23.78</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>24.73</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>25.19</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>24.73</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>25.19</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>12865818.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>10985371.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>10985371.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>12800305.9</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>20490499.5</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>20490499.5</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-2189713.468717266</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>12865818</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>12865818.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>23.65</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>24.75</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>25.22</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>7609682.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>11668266.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>11668266.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>12292382.1</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>20577790.8</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>20577790.8</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-2573496.353847314</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>7609682</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>7609682.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>23.7</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>24.8</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>25.26</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>25.26</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>8801880.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>13371563.4</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>13371563.4</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>12043049.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>20662476.86</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>20662476.86</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-2466689.60568141</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>8801880</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>8801880.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>24.02</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>24.88</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>25.32</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>25.32</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>11442166.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>14617168.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>14617168.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>11589868.0</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>20686354.56</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>20686354.56</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-2353747.979527211</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>11442166</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>11442166.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>24.31</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>24.95</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>25.38</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>25.38</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>14207313.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>14477573.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>14477573</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>11107938.7</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>20581952.4</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>20581952.4</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-2391228.157180952</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>14207313</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>14207313.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>24.66</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>25.04</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>25.04</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>25.44</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>16280290.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>14615240.0</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>14615240</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>10596820.3</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>20406059.64</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>20406059.64</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-2655636.01250126</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>16280290</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>16280290.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>24.87</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>25.11</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>25.5</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>25.11</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>25.5</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>16126168.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>12916498.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>12916498</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>9888875.8</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>20173044.84</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>20173044.84</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-3160622.055369517</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>16126168</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>16126168.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>24.99</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>25.16</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>25.54</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>25.16</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>25.54</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>15029906.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>10714534.6</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>10714534.6</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>9605809.5</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>19982259.56</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>19982259.56</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-3752638.257489543</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>15029906</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>15029906.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>25.02</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>25.2</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>25.58</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>10744188.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>8562567.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>8562567.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>11331619.6</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>19841028.7</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>19841028.7</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-4346896.251322096</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>10744188</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>10744188.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>25.21</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>25.21</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>25.62</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>14895648.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>7738304.4</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>7738304.4</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>26170087.4</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>19799430.9</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>19799430.9</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-4581405.87639281</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>14895648</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>14895648.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>53.98</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>53.97</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>53.93</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>53.97</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>53.93</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>309731502.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>149304115.8</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>149304115.8</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>110162521.1</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>117855603.56</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>117855603.56</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>16654678.1665608</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>309731502</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>309731502.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>52.7</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>53.86</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>218314058.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>106744330.4</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>106744330.4</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>89222972.2</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>113419591.14</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>113419591.14</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>1495019.715925276</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>218314058</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>218314058.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>51.73999999999999</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>53.8</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>48571438.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>72818195.4</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>72818195.40000001</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>81980229.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>111872773.36</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>111872773.36</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-10420302.63197996</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>48571438</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>48571438.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>51.66</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>53.95</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>53.87</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>53.95</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>53.87</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>87014812.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>72647562.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>72647562.40000001</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>80519028.5</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>111823206.94</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>111823206.94</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-8883328.749273852</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>87014812</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>87014812.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>51.86</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>54.22</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>53.88</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>54.22</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>53.88</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>82888769.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>74426138.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>74426138.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>77212396.3</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>110830557.88</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>110830557.88</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-10489322.96150535</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>82888769</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>82888769.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>51.62</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>54.38</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>53.86</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>54.38</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>53.86</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>96932575.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>71020926.4</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>71020926.40000001</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>72937143.1</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>109856642.7</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>109856642.7</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-11966905.69463946</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>96932575</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>96932575.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>51.84</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>54.65</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>53.89</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>53.89</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>48683383.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>71701614.0</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>71701614</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>70664021.5</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>108733892.34</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>108733892.34</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-15155042.18145107</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>48683383</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>48683383.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>52.0</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>54.93</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>54.93</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>47718273.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>91142263.0</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>91142263</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>73006397.7</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>108974522.54</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>108974522.54</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-13998715.08470152</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>47718273</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>47718273.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>52.58</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>55.22</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>53.9</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>95907691.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>88390494.6</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>88390494.59999999</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>76185022.6</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>108723394.98</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>108723394.98</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-11743460.47917713</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>95907691</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>95907691.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>53.06</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>55.56</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>53.91</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>55.56</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>53.91</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>65862710.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>79998654.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>79998654.40000001</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>103628419.5</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>108329575.64</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>108329575.64</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-13265410.81131452</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>65862710</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>65862710.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>53.67999999999999</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>55.84</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>53.96</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>55.84</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>53.96</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>100336013.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>74853359.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>74853359.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>154411688.0</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>108348566.82</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>108348566.82</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-11746755.79253529</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>100336013</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>100336013.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39239,11 +38711,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
           <t>2611</t>
@@ -39425,41 +38893,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
+      <c r="AM90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
+      <c r="AP90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT90" t="inlineStr">
         <is>
           <t>0</t>
@@ -39480,20 +38944,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>0</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>0</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38970,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>0</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39139,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39323,11 @@
           <t>58.14</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>57.65</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>50.76</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>50.76</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39374,16 @@
           <t>56864083.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>49667804.4</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>49667804.4</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>55100193.4</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>65077891.96</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>65077891.96</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39400,10 @@
           <t>-1281965.690591685</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>56864083</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>56864083.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39753,11 @@
           <t>57.72000000000001</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>57.62</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>50.25</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>57.62</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>50.25</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39804,16 @@
           <t>34267315.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>50744106.4</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>50744106.4</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>54082868.7</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>64807510.26</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>64807510.26</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39830,10 @@
           <t>-1866398.578095213</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>34267315</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>34267315.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +39999,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40183,11 @@
           <t>57.32000000000001</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>57.58</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>49.75</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>57.58</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>49.75</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40234,16 @@
           <t>57923106.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>66727550.4</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>66727550.4</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>54074047.8</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>65417577.8</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>65417577.8</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40260,10 @@
           <t>-213563.3253111318</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>57923106</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>57923106.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40429,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40613,11 @@
           <t>57.17999999999999</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>57.56</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>49.27</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>57.56</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>49.27</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40664,16 @@
           <t>53259597.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>64935816.2</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>64935816.2</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>53469700.0</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>65166202.68</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>65166202.68</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40690,10 @@
           <t>-379291.8811441883</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>53259597</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>53259597.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40859,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41043,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>57.51</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>48.8</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>57.51</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>48.8</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41094,16 @@
           <t>46024921.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>62159314.6</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>62159314.6</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>50977637.5</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>65142686.74</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>65142686.74</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41120,10 @@
           <t>-102839.1437219754</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>46024921</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>46024921.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41289,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41473,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>57.45</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>48.34</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>48.34</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41524,16 @@
           <t>62245593.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>60532582.4</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>60532582.4</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>52060465.0</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>65076480.76</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>65076480.76</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41550,10 @@
           <t>1070910.022014104</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>62245593</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>62245593.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41719,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41903,11 @@
           <t>56.94</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>57.42</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>47.88</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>47.88</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41954,16 @@
           <t>114184535.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>57421631.0</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>57421631</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>51090635.9</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>65160318.42</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>65160318.42</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41980,10 @@
           <t>971518.6151365787</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>114184535</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>114184535.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42149,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42333,11 @@
           <t>57.02</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>47.45</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>47.45</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42384,16 @@
           <t>48964435.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>41420545.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>41420545.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>44543610.7</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>65562718.96</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>65562718.96</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42410,10 @@
           <t>-4770052.845229052</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>48964435</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>48964435.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42579,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42763,11 @@
           <t>57.08</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>57.5</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>47.01</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>47.01</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42814,16 @@
           <t>39377089.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>42003583.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>42003583.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>42069892.1</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>66086974.4</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>66086974.4</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42840,10 @@
           <t>-5814070.901278906</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>39377089</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>39377089.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43009,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43193,11 @@
           <t>57.36</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>57.61</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>46.57</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>57.61</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>46.57</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43244,16 @@
           <t>37891260.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>39795960.4</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>39795960.4</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>44332954.5</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>66156768.56</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>66156768.56</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43270,10 @@
           <t>-6070664.23487588</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>37891260</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>37891260.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
@@ -44037,7 +43439,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -44221,15 +43623,11 @@
           <t>57.73999999999999</t>
         </is>
       </c>
-      <c r="AM101" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
-      </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>46.14</t>
-        </is>
+      <c r="AM101" t="n">
+        <v>57.69</v>
+      </c>
+      <c r="AN101" t="n">
+        <v>46.14</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
@@ -44276,20 +43674,16 @@
           <t>46690836.0</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
-        <is>
-          <t>43588347.6</t>
-        </is>
+      <c r="AX101" t="n">
+        <v>43588347.6</v>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
           <t>51191973.7</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
-        <is>
-          <t>66777211.68</t>
-        </is>
+      <c r="AZ101" t="n">
+        <v>66777211.68</v>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
@@ -44306,8 +43700,10 @@
           <t>-6061220.738768853</t>
         </is>
       </c>
-      <c r="BD101" t="n">
-        <v>46690836</v>
+      <c r="BD101" t="inlineStr">
+        <is>
+          <t>46690836.0</t>
+        </is>
       </c>
       <c r="BE101" t="inlineStr">
         <is>
@@ -44473,7 +43869,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -44657,15 +44053,11 @@
           <t>13.65</t>
         </is>
       </c>
-      <c r="AM102" t="inlineStr">
-        <is>
-          <t>13.34</t>
-        </is>
-      </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>13.32</t>
-        </is>
+      <c r="AM102" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="AN102" t="n">
+        <v>13.32</v>
       </c>
       <c r="AO102" t="inlineStr">
         <is>
@@ -44712,20 +44104,16 @@
           <t>4314746.0</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
-        <is>
-          <t>4978301.4</t>
-        </is>
+      <c r="AX102" t="n">
+        <v>4978301.4</v>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
           <t>4517684.3</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
-        <is>
-          <t>4713760.62</t>
-        </is>
+      <c r="AZ102" t="n">
+        <v>4713760.62</v>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
@@ -44742,8 +44130,10 @@
           <t>27641.80035279691</t>
         </is>
       </c>
-      <c r="BD102" t="n">
-        <v>4314746</v>
+      <c r="BD102" t="inlineStr">
+        <is>
+          <t>4314746.0</t>
+        </is>
       </c>
       <c r="BE102" t="inlineStr">
         <is>
@@ -44909,7 +44299,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -45093,15 +44483,11 @@
           <t>13.53</t>
         </is>
       </c>
-      <c r="AM103" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
-      </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM103" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="AN103" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
@@ -45148,20 +44534,16 @@
           <t>2757942.0</t>
         </is>
       </c>
-      <c r="AX103" t="inlineStr">
-        <is>
-          <t>4746919.2</t>
-        </is>
+      <c r="AX103" t="n">
+        <v>4746919.2</v>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
           <t>4730599.7</t>
         </is>
       </c>
-      <c r="AZ103" t="inlineStr">
-        <is>
-          <t>4734328.96</t>
-        </is>
+      <c r="AZ103" t="n">
+        <v>4734328.96</v>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
@@ -45178,8 +44560,10 @@
           <t>64481.15028462093</t>
         </is>
       </c>
-      <c r="BD103" t="n">
-        <v>2757942</v>
+      <c r="BD103" t="inlineStr">
+        <is>
+          <t>2757942.0</t>
+        </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
@@ -45345,7 +44729,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -45529,15 +44913,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
-      </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>13.31</t>
-        </is>
+      <c r="AM104" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>13.31</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -45584,20 +44964,16 @@
           <t>8651275.0</t>
         </is>
       </c>
-      <c r="AX104" t="inlineStr">
-        <is>
-          <t>5201761.4</t>
-        </is>
+      <c r="AX104" t="n">
+        <v>5201761.4</v>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
           <t>4754039.1</t>
         </is>
       </c>
-      <c r="AZ104" t="inlineStr">
-        <is>
-          <t>4800272.02</t>
-        </is>
+      <c r="AZ104" t="n">
+        <v>4800272.02</v>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
@@ -45614,8 +44990,10 @@
           <t>281606.3233913472</t>
         </is>
       </c>
-      <c r="BD104" t="n">
-        <v>8651275</v>
+      <c r="BD104" t="inlineStr">
+        <is>
+          <t>8651275.0</t>
+        </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
@@ -45781,7 +45159,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -45965,15 +45343,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM105" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>13.3</t>
-        </is>
+      <c r="AM105" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN105" t="n">
+        <v>13.3</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -46020,20 +45394,16 @@
           <t>3707868.0</t>
         </is>
       </c>
-      <c r="AX105" t="inlineStr">
-        <is>
-          <t>4136832.8</t>
-        </is>
+      <c r="AX105" t="n">
+        <v>4136832.8</v>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
           <t>4711853.8</t>
         </is>
       </c>
-      <c r="AZ105" t="inlineStr">
-        <is>
-          <t>4713576.58</t>
-        </is>
+      <c r="AZ105" t="n">
+        <v>4713576.58</v>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
@@ -46050,8 +45420,10 @@
           <t>-49700.76229159161</t>
         </is>
       </c>
-      <c r="BD105" t="n">
-        <v>3707868</v>
+      <c r="BD105" t="inlineStr">
+        <is>
+          <t>3707868.0</t>
+        </is>
       </c>
       <c r="BE105" t="inlineStr">
         <is>
@@ -46217,7 +45589,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -46401,15 +45773,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM106" t="inlineStr">
-        <is>
-          <t>13.24</t>
-        </is>
-      </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM106" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="AN106" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -46456,20 +45824,16 @@
           <t>5459676.0</t>
         </is>
       </c>
-      <c r="AX106" t="inlineStr">
-        <is>
-          <t>4186896.0</t>
-        </is>
+      <c r="AX106" t="n">
+        <v>4186896</v>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
           <t>4402878.9</t>
         </is>
       </c>
-      <c r="AZ106" t="inlineStr">
-        <is>
-          <t>4751543.98</t>
-        </is>
+      <c r="AZ106" t="n">
+        <v>4751543.98</v>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
@@ -46486,8 +45850,10 @@
           <t>8429.178243194707</t>
         </is>
       </c>
-      <c r="BD106" t="n">
-        <v>5459676</v>
+      <c r="BD106" t="inlineStr">
+        <is>
+          <t>5459676.0</t>
+        </is>
       </c>
       <c r="BE106" t="inlineStr">
         <is>
@@ -46653,7 +46019,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -46837,15 +46203,11 @@
           <t>13.41</t>
         </is>
       </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM107" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AN107" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -46892,20 +46254,16 @@
           <t>3157835.0</t>
         </is>
       </c>
-      <c r="AX107" t="inlineStr">
-        <is>
-          <t>4057067.2</t>
-        </is>
+      <c r="AX107" t="n">
+        <v>4057067.2</v>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
           <t>4239221.2</t>
         </is>
       </c>
-      <c r="AZ107" t="inlineStr">
-        <is>
-          <t>5062110.22</t>
-        </is>
+      <c r="AZ107" t="n">
+        <v>5062110.22</v>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
@@ -46922,8 +46280,10 @@
           <t>-96522.80593008175</t>
         </is>
       </c>
-      <c r="BD107" t="n">
-        <v>3157835</v>
+      <c r="BD107" t="inlineStr">
+        <is>
+          <t>3157835.0</t>
+        </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
@@ -47089,7 +46449,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -47273,15 +46633,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM108" t="inlineStr">
-        <is>
-          <t>13.23</t>
-        </is>
-      </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM108" t="n">
+        <v>13.23</v>
+      </c>
+      <c r="AN108" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -47328,20 +46684,16 @@
           <t>5032153.0</t>
         </is>
       </c>
-      <c r="AX108" t="inlineStr">
-        <is>
-          <t>4714280.2</t>
-        </is>
+      <c r="AX108" t="n">
+        <v>4714280.2</v>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
           <t>4265300.7</t>
         </is>
       </c>
-      <c r="AZ108" t="inlineStr">
-        <is>
-          <t>5387852.96</t>
-        </is>
+      <c r="AZ108" t="n">
+        <v>5387852.96</v>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
@@ -47358,8 +46710,10 @@
           <t>3618.852605597116</t>
         </is>
       </c>
-      <c r="BD108" t="n">
-        <v>5032153</v>
+      <c r="BD108" t="inlineStr">
+        <is>
+          <t>5032153.0</t>
+        </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
@@ -47525,7 +46879,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -47709,15 +47063,11 @@
           <t>13.47</t>
         </is>
       </c>
-      <c r="AM109" t="inlineStr">
-        <is>
-          <t>13.22</t>
-        </is>
-      </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>13.29</t>
-        </is>
+      <c r="AM109" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="AN109" t="n">
+        <v>13.29</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -47764,20 +47114,16 @@
           <t>3326632.0</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
-        <is>
-          <t>4306316.8</t>
-        </is>
+      <c r="AX109" t="n">
+        <v>4306316.8</v>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
           <t>4483139.7</t>
         </is>
       </c>
-      <c r="AZ109" t="inlineStr">
-        <is>
-          <t>5335377.72</t>
-        </is>
+      <c r="AZ109" t="n">
+        <v>5335377.72</v>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
@@ -47794,8 +47140,10 @@
           <t>-54270.66565077566</t>
         </is>
       </c>
-      <c r="BD109" t="n">
-        <v>3326632</v>
+      <c r="BD109" t="inlineStr">
+        <is>
+          <t>3326632.0</t>
+        </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
@@ -47961,7 +47309,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -48145,15 +47493,11 @@
           <t>13.46</t>
         </is>
       </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>13.21</t>
-        </is>
-      </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
+      <c r="AM110" t="n">
+        <v>13.21</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>13.28</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -48200,20 +47544,16 @@
           <t>3958184.0</t>
         </is>
       </c>
-      <c r="AX110" t="inlineStr">
-        <is>
-          <t>5286874.8</t>
-        </is>
+      <c r="AX110" t="n">
+        <v>5286874.8</v>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
           <t>4828292.4</t>
         </is>
       </c>
-      <c r="AZ110" t="inlineStr">
-        <is>
-          <t>5326099.52</t>
-        </is>
+      <c r="AZ110" t="n">
+        <v>5326099.52</v>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
@@ -48230,8 +47570,10 @@
           <t>47702.65347050503</t>
         </is>
       </c>
-      <c r="BD110" t="n">
-        <v>3958184</v>
+      <c r="BD110" t="inlineStr">
+        <is>
+          <t>3958184.0</t>
+        </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
@@ -48397,7 +47739,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -48581,15 +47923,11 @@
           <t>13.4</t>
         </is>
       </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>13.2</t>
-        </is>
-      </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>13.28</t>
-        </is>
+      <c r="AM111" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>13.28</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -48636,20 +47974,16 @@
           <t>4810532.0</t>
         </is>
       </c>
-      <c r="AX111" t="inlineStr">
-        <is>
-          <t>4618861.8</t>
-        </is>
+      <c r="AX111" t="n">
+        <v>4618861.8</v>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
           <t>5030972.5</t>
         </is>
       </c>
-      <c r="AZ111" t="inlineStr">
-        <is>
-          <t>5401520.16</t>
-        </is>
+      <c r="AZ111" t="n">
+        <v>5401520.16</v>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
@@ -48666,8 +48000,10 @@
           <t>124008.8717341041</t>
         </is>
       </c>
-      <c r="BD111" t="n">
-        <v>4810532</v>
+      <c r="BD111" t="inlineStr">
+        <is>
+          <t>4810532.0</t>
+        </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
@@ -48833,7 +48169,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -49017,15 +48353,11 @@
           <t>13.34</t>
         </is>
       </c>
-      <c r="AM112" t="inlineStr">
-        <is>
-          <t>13.18</t>
-        </is>
-      </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>13.27</t>
-        </is>
+      <c r="AM112" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="AN112" t="n">
+        <v>13.27</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -49072,20 +48404,16 @@
           <t>6443900.0</t>
         </is>
       </c>
-      <c r="AX112" t="inlineStr">
-        <is>
-          <t>4421375.2</t>
-        </is>
+      <c r="AX112" t="n">
+        <v>4421375.2</v>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
           <t>4897374.1</t>
         </is>
       </c>
-      <c r="AZ112" t="inlineStr">
-        <is>
-          <t>5403235.3</t>
-        </is>
+      <c r="AZ112" t="n">
+        <v>5403235.3</v>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
@@ -49102,8 +48430,10 @@
           <t>137265.8666915996</t>
         </is>
       </c>
-      <c r="BD112" t="n">
-        <v>6443900</v>
+      <c r="BD112" t="inlineStr">
+        <is>
+          <t>6443900.0</t>
+        </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
